--- a/data/Goblins.xlsx
+++ b/data/Goblins.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>goblinID</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>coin</t>
+  </si>
+  <si>
+    <t>exp</t>
   </si>
   <si>
     <t>moveSpeed</t>
@@ -1174,19 +1177,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G10"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="6"/>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
     <col min="3" max="3" width="15.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="11.4444444444444" customWidth="1"/>
-    <col min="5" max="5" width="16.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="4" max="5" width="11.4444444444444" customWidth="1"/>
+    <col min="6" max="6" width="16.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1208,42 +1211,48 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="D2" t="s">
+      <c r="H2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -1254,18 +1263,21 @@
       <c r="G3" t="s">
         <v>16</v>
       </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5">
         <v>5</v>
@@ -1274,21 +1286,24 @@
         <v>1</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>19</v>
       </c>
       <c r="G5" t="s">
         <v>20</v>
       </c>
+      <c r="H5" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>10</v>
@@ -1297,21 +1312,24 @@
         <v>2</v>
       </c>
       <c r="E6">
+        <v>2</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>22</v>
-      </c>
       <c r="G6" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7">
         <v>15</v>
@@ -1320,21 +1338,24 @@
         <v>3</v>
       </c>
       <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
-        <v>24</v>
-      </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8">
         <v>20</v>
@@ -1343,21 +1364,24 @@
         <v>4</v>
       </c>
       <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
         <v>10</v>
       </c>
-      <c r="F8" t="s">
-        <v>26</v>
-      </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>50</v>
@@ -1366,21 +1390,24 @@
         <v>10</v>
       </c>
       <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
         <v>8</v>
       </c>
-      <c r="F9" t="s">
-        <v>28</v>
-      </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>29</v>
+      </c>
+      <c r="H9" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C10">
         <v>80</v>
@@ -1389,13 +1416,16 @@
         <v>25</v>
       </c>
       <c r="E10">
+        <v>25</v>
+      </c>
+      <c r="F10">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
-        <v>30</v>
-      </c>
       <c r="G10" t="s">
-        <v>20</v>
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
